--- a/output/pdf_financials_xlsx/HIDE.xlsx
+++ b/output/pdf_financials_xlsx/HIDE.xlsx
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.034294</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.020849</v>
       </c>
     </row>
     <row r="93">
@@ -2472,7 +2472,11 @@
           <t>Reserves (Note 4)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="n">
         <v>0.034294</v>
       </c>

--- a/output/pdf_financials_xlsx/HIDE.xlsx
+++ b/output/pdf_financials_xlsx/HIDE.xlsx
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.145966</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.06361600000000001</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.145966</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.06361600000000001</v>
       </c>
     </row>
     <row r="37">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/HIDE.xlsx
+++ b/output/pdf_financials_xlsx/HIDE.xlsx
@@ -514,10 +514,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.006375</v>
+        <v>0.014644</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.019552</v>
+        <v>0.034038</v>
       </c>
     </row>
     <row r="8">
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.007835999999999999</v>
+        <v>0.016105</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.021986</v>
+        <v>0.036472</v>
       </c>
     </row>
     <row r="11">
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.007835999999999999</v>
+        <v>-0.016105</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.021986</v>
+        <v>-0.036472</v>
       </c>
     </row>
     <row r="12">
@@ -2920,7 +2920,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
         <v>0.008269</v>
       </c>
